--- a/04-artefactos-tecnicos/04.03-requisitos-e-rtm/m2-requirements-traceability-matrix-v01.xlsx
+++ b/04-artefactos-tecnicos/04.03-requisitos-e-rtm/m2-requirements-traceability-matrix-v01.xlsx
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>I020; I051; I054; I075</t>
+          <t>I020; I051; I054; I063; I064; I065; I075; I080; I081</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Alterar a própria palavra-passe</t>
+          <t>Alterar a própria palavra-passe (Candidato)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>I020; I026; I043; I044; I052; I075</t>
+          <t>I020; I026; I043; I044; I052; I063; I064; I065; I075; I080; I081</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>I020; I026; I052; I075</t>
+          <t>I020; I026; I052; I063; I064; I065; I075; I080; I081</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>I020; I026; I052; I075</t>
+          <t>I020; I026; I052; I063; I064; I065; I075; I080; I081</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>I020; I044; I077</t>
+          <t>I020; I044; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>I020; I044; I077</t>
+          <t>I020; I044; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>I020; I049; I077</t>
+          <t>I020; I049; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>I020; I049; I077</t>
+          <t>I020; I049; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>I020; I077</t>
+          <t>I020; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>I020; I077</t>
+          <t>I020; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>I020; I077</t>
+          <t>I020; I063; I064; I065; I077; I080; I081</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I059; I076</t>
+          <t>I020; I030; I059; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I059; I076</t>
+          <t>I020; I030; I059; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I059</t>
+          <t>I020; I030; I059; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I059; I076</t>
+          <t>I020; I030; I059; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I057; I076</t>
+          <t>I020; I030; I057; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I050; I057; I076</t>
+          <t>I020; I030; I050; I057; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I057; I061; I076</t>
+          <t>I020; I030; I057; I061; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I061</t>
+          <t>I020; I030; I061; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>I020; I030; I061; I076</t>
+          <t>I020; I030; I061; I063; I064; I065; I076; I080; I081</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>I020; I030</t>
+          <t>I020; I030; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>I020; I078</t>
+          <t>I020; I063; I064; I065; I078; I080; I081</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>I020; I078</t>
+          <t>I020; I063; I064; I065; I078; I080; I081</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Consultar a lista de conversas</t>
+          <t>Consultar a lista de conversas (Candidato)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Consultar o histórico de uma conversa</t>
+          <t>Consultar o histórico de uma conversa (Candidato)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Receber mensagens sem atualização manual</t>
+          <t>Receber mensagens sem atualização manual (Candidato)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Encerrar uma conversa</t>
+          <t>Encerrar uma conversa (Candidato)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>I020; I031</t>
+          <t>I020; I031; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>I020; I030</t>
+          <t>I020; I030; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Consultar a área de notificações</t>
+          <t>Consultar a área de notificações (Candidato)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Marcar notificação como lida</t>
+          <t>Marcar notificação como lida (Candidato)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Aceder ao elemento associado à notificação</t>
+          <t>Aceder ao elemento associado à notificação (Candidato)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I043; I046; I053; I069</t>
+          <t>I021; I027; I043; I046; I053; I063; I064; I065; I069; I079; I081</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Iniciar sessão na área de gestão web</t>
+          <t>Iniciar sessão na área de gestão web (Recrutador)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>I021; I051; I054; I069</t>
+          <t>I021; I051; I054; I063; I064; I065; I069; I079; I081</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>I021; I029</t>
+          <t>I021; I029; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Alterar a própria palavra-passe</t>
+          <t>Alterar a própria palavra-passe (Recrutador)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I045; I053</t>
+          <t>I021; I027; I045; I053; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I053</t>
+          <t>I021; I027; I053; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I053</t>
+          <t>I021; I027; I053; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I053</t>
+          <t>I021; I027; I053; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>I021; I027; I053</t>
+          <t>I021; I027; I053; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>I021; I045</t>
+          <t>I021; I045; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>I021; I045</t>
+          <t>I021; I045; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>I021; I045</t>
+          <t>I021; I045; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>I021; I045</t>
+          <t>I021; I045; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>I021; I029; I048; I056; I070</t>
+          <t>I021; I029; I048; I056; I063; I064; I065; I070; I079; I081</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>I021; I029; I056; I070</t>
+          <t>I021; I029; I056; I063; I064; I065; I070; I079; I081</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>I021; I029; I070</t>
+          <t>I021; I029; I063; I064; I065; I070; I079; I081</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>I021; I029; I056; I070</t>
+          <t>I021; I029; I056; I063; I064; I065; I070; I079; I081</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>I021; I032; I060; I071</t>
+          <t>I021; I032; I060; I063; I064; I065; I071; I079; I081</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>I021; I032; I072</t>
+          <t>I021; I032; I063; I064; I065; I072; I079; I081</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>I021; I032; I049; I072</t>
+          <t>I021; I032; I049; I063; I064; I065; I072; I079; I081</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>I021; I031; I058; I072</t>
+          <t>I021; I031; I058; I063; I064; I065; I072; I079; I081</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>I021; I031; I058; I072</t>
+          <t>I021; I031; I058; I063; I064; I065; I072; I079; I081</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>I021; I031; I050; I058</t>
+          <t>I021; I031; I050; I058; I063; I064; I065; I081</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>I021; I031; I050; I058</t>
+          <t>I021; I031; I050; I058; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>I021; I031</t>
+          <t>I021; I031; I063; I064; I065; I079; I080; I081</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I080; I081</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Consultar a lista de conversas</t>
+          <t>Consultar a lista de conversas (Recrutador)</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Consultar o histórico de uma conversa</t>
+          <t>Consultar o histórico de uma conversa (Recrutador)</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Receber mensagens sem atualização manual</t>
+          <t>Receber mensagens sem atualização manual (Recrutador)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Encerrar uma conversa</t>
+          <t>Encerrar uma conversa (Recrutador)</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I080; I081</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>I021; I030</t>
+          <t>I021; I030; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>I021; I031</t>
+          <t>I021; I031; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>I021; I028</t>
+          <t>I021; I028; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Consultar a área de notificações</t>
+          <t>Consultar a área de notificações (Recrutador)</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Marcar notificação como lida</t>
+          <t>Marcar notificação como lida (Recrutador)</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Aceder ao elemento associado à notificação</t>
+          <t>Aceder ao elemento associado à notificação (Recrutador)</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Iniciar sessão na área de gestão web</t>
+          <t>Iniciar sessão na área de gestão web (Administrador)</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>I022; I051; I054; I069</t>
+          <t>I022; I047; I051; I054; I063; I064; I065; I069; I079; I081</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Alterar a própria palavra-passe</t>
+          <t>Alterar a própria palavra-passe (Administrador)</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>I022; I028; I055; I073</t>
+          <t>I022; I028; I047; I055; I063; I064; I065; I073; I079; I081</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>I022; I028; I055; I073</t>
+          <t>I022; I028; I047; I055; I063; I064; I065; I073; I079; I081</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>I022; I028; I055; I073</t>
+          <t>I022; I028; I047; I055; I063; I064; I065; I073; I079; I081</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>I022; I028; I055; I073</t>
+          <t>I022; I028; I047; I055; I063; I064; I065; I073; I079; I081</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>I022; I074</t>
+          <t>I022; I047; I063; I064; I065; I074; I079; I081</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>I022; I062</t>
+          <t>I022; I047; I062; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>I022; I062</t>
+          <t>I022; I047; I062; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>I020; I051; I075</t>
+          <t>I020; I051; I063; I064; I065; I075; I080; I081</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Terminar sessão na área de gestão web</t>
+          <t>Terminar sessão na área de gestão web (Recrutador)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>I021; I051; I069</t>
+          <t>I021; I051; I063; I064; I065; I069; I079; I081</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Terminar sessão na área de gestão web</t>
+          <t>Terminar sessão na área de gestão web (Administrador)</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>I022; I051; I069</t>
+          <t>I022; I047; I051; I063; I064; I065; I069; I079; I081</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Marcar como lidas as mensagens ao abrir a conversa</t>
+          <t>Marcar como lidas as mensagens ao abrir a conversa (Candidato)</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Marcar como lidas as mensagens ao abrir a conversa</t>
+          <t>Marcar como lidas as mensagens ao abrir a conversa (Recrutador)</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Receber notificações sem atualização manual</t>
+          <t>Receber notificações sem atualização manual (Candidato)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>I020</t>
+          <t>I020; I063; I064; I065; I080; I081</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Receber notificações sem atualização manual</t>
+          <t>Receber notificações sem atualização manual (Recrutador)</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>I021</t>
+          <t>I021; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I081</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>I021; I030; I032; I050; I060</t>
+          <t>I021; I030; I032; I050; I060; I063; I064; I065; I081</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>I021; I056</t>
+          <t>I021; I056; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>I022</t>
+          <t>I022; I047; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>I021; I031; I058</t>
+          <t>I021; I031; I058; I063; I064; I065; I079; I081</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>I021; I032; I050</t>
+          <t>I021; I032; I050; I063; I064; I065; I081</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I063; I064; I065</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>I023; I030</t>
+          <t>I023; I030; I063; I064; I065; I080</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>I023; I026; I027</t>
+          <t>I023; I026; I027; I063; I064; I065</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>I023; I051</t>
+          <t>I023; I051; I063; I064; I065</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>I023; I051</t>
+          <t>I023; I051; I063; I064; I065</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>I023; I051</t>
+          <t>I023; I051; I063; I064; I065</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>I023; I032</t>
+          <t>I023; I032; I063; I064; I065</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>I023; I026; I027; I029</t>
+          <t>I023; I026; I027; I029; I063; I064; I065</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>I023; I054</t>
+          <t>I023; I054; I063; I064; I065</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>I023; I030</t>
+          <t>I023; I030; I080</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>I023; I030</t>
+          <t>I023; I030; I080</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I079</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I042; I063; I064; I065</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I080</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>I023; I029</t>
+          <t>I023; I029; I063; I064; I065</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>I023; I029</t>
+          <t>I023; I029; I063; I064; I065</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I063; I064; I065</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>I023</t>
+          <t>I023; I079</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -9531,7 +9531,6 @@
       <c r="K153" s="28" t="n"/>
       <c r="L153" s="29" t="n"/>
     </row>
-    <row r="154"/>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="10" t="inlineStr">
         <is>
@@ -9620,9 +9619,9 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A150:C150"/>
     <mergeCell ref="A2:L4"/>
+    <mergeCell ref="D152:L152"/>
     <mergeCell ref="D8:L8"/>
     <mergeCell ref="F10:I10"/>
-    <mergeCell ref="D152:L152"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A155:L155"/>

--- a/04-artefactos-tecnicos/04.03-requisitos-e-rtm/m2-requirements-traceability-matrix-v01.xlsx
+++ b/04-artefactos-tecnicos/04.03-requisitos-e-rtm/m2-requirements-traceability-matrix-v01.xlsx
@@ -867,7 +867,7 @@
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>m2-especificacao-requisitos-v02.md</t>
+          <t>m2-especificacao-requisitos-v01.md</t>
         </is>
       </c>
       <c r="E7" s="28" t="n"/>
@@ -889,7 +889,7 @@
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>m2-checklist-aprovacao-requisitos-v01.xlsx</t>
+          <t>m2-checklist-aprovacao-requisitos-v02.xlsx</t>
         </is>
       </c>
       <c r="E8" s="28" t="n"/>
